--- a/Doc/导出配置/Map.xlsx
+++ b/Doc/导出配置/Map.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7835EE-04AD-4547-8D42-AC7FF90481C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD75275-B9A1-419E-85AD-54A0336C1BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
   </bookViews>
@@ -162,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{605F7AE0-C47F-4124-930A-B9249B87C490}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{605F7AE0-C47F-4124-930A-B9249B87C490}">
       <text>
         <r>
           <rPr>
@@ -182,7 +182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{3FD22595-2D89-4707-8C08-599ADD0E78F7}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{3FD22595-2D89-4707-8C08-599ADD0E78F7}">
       <text>
         <r>
           <rPr>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -303,10 +303,6 @@
     <t>先天</t>
   </si>
   <si>
-    <t>先天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>修真</t>
   </si>
   <si>
@@ -314,10 +310,6 @@
   </si>
   <si>
     <t>修神</t>
-  </si>
-  <si>
-    <t>@p_fzaf/image/bg.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>类型</t>
@@ -344,56 +336,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>先天_一品</t>
-  </si>
-  <si>
-    <t>先天_一品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先天_二品</t>
-  </si>
-  <si>
-    <t>先天_二品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先天_一品分支1</t>
-  </si>
-  <si>
-    <t>先天_一品分支1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先天_三品</t>
-  </si>
-  <si>
-    <t>先天_四品</t>
-  </si>
-  <si>
-    <t>先天_五品</t>
-  </si>
-  <si>
-    <t>先天_六品</t>
-  </si>
-  <si>
-    <t>先天_七品</t>
-  </si>
-  <si>
-    <t>先天_八品</t>
-  </si>
-  <si>
-    <t>先天_九品</t>
-  </si>
-  <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>先天_无品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>索引</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -401,42 +347,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>先天_无品</t>
-  </si>
-  <si>
-    <t>先天_一品to先天_无品</t>
-  </si>
-  <si>
-    <t>先天_一品分支1to先天_无品</t>
-  </si>
-  <si>
-    <t>先天_二品to先天_一品</t>
-  </si>
-  <si>
-    <t>先天_二品to先天_一品分支1</t>
-  </si>
-  <si>
-    <t>先天_三品to先天_二品</t>
-  </si>
-  <si>
-    <t>先天_四品to先天_三品</t>
-  </si>
-  <si>
-    <t>先天_五品to先天_四品</t>
-  </si>
-  <si>
-    <t>先天_六品to先天_五品</t>
-  </si>
-  <si>
-    <t>先天_七品to先天_六品</t>
-  </si>
-  <si>
-    <t>先天_八品to先天_七品</t>
-  </si>
-  <si>
-    <t>先天_九品to先天_八品</t>
-  </si>
-  <si>
     <t>x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -477,6 +387,63 @@
   </si>
   <si>
     <t>guai11</t>
+  </si>
+  <si>
+    <t>bg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分支</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后天2品分支1</t>
+  </si>
+  <si>
+    <t>后天3品分支1</t>
+  </si>
+  <si>
+    <t>后天4品分支1</t>
+  </si>
+  <si>
+    <t>后天5品分支1</t>
+  </si>
+  <si>
+    <t>后天6品分支1</t>
+  </si>
+  <si>
+    <t>后天7品分支1</t>
+  </si>
+  <si>
+    <t>后天8品分支1</t>
+  </si>
+  <si>
+    <t>后天9品分支1</t>
+  </si>
+  <si>
+    <t>后天10品分支1</t>
+  </si>
+  <si>
+    <t>后天10品分支2</t>
+  </si>
+  <si>
+    <t>后天1品分支1</t>
+  </si>
+  <si>
+    <t>guai12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后天11品分支1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -547,7 +514,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="27">
     <dxf>
       <font>
         <b val="0"/>
@@ -591,6 +558,57 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -621,74 +639,76 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -725,59 +745,44 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -997,7 +1002,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C2E19C6-8F99-47B9-A18E-66BEAC16B0C5}" name="Cfg_Map" displayName="Cfg_Map" ref="A1:E7" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C2E19C6-8F99-47B9-A18E-66BEAC16B0C5}" name="Cfg_Map" displayName="Cfg_Map" ref="A1:E7" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:E7" xr:uid="{8C2E19C6-8F99-47B9-A18E-66BEAC16B0C5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1006,19 +1011,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="9" xr3:uid="{E6B9AA54-B5B9-4C54-BED2-09D9E8A57723}" name="索引" dataDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{62A7661E-46D3-4FBD-A598-40D05FDEA174}" name="id" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{8202C8E8-3ECF-44AC-906A-08BC887BC701}" name="名称" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{AA7B6830-77D3-45E0-81B3-CDB5D3D75B6A}" name="背景图片" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{493917F0-DAA9-436F-900A-1A87EE584419}" name="挂机点列表" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{E6B9AA54-B5B9-4C54-BED2-09D9E8A57723}" name="索引" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{62A7661E-46D3-4FBD-A598-40D05FDEA174}" name="id" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{8202C8E8-3ECF-44AC-906A-08BC887BC701}" name="名称" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{AA7B6830-77D3-45E0-81B3-CDB5D3D75B6A}" name="背景图片" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{493917F0-DAA9-436F-900A-1A87EE584419}" name="挂机点列表" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}" name="Cfg_MapPoint" displayName="Cfg_MapPoint" ref="A1:I13" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:I13" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}" name="Cfg_MapPoint" displayName="Cfg_MapPoint" ref="A1:K14" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:K14" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1028,25 +1033,29 @@
     <filterColumn colId="6" hiddenButton="1"/>
     <filterColumn colId="7" hiddenButton="1"/>
     <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="9">
-    <tableColumn id="12" xr3:uid="{5D994712-7AAB-4B73-A5A5-81E04ACECD89}" name="索引" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{B083A4F3-A0E0-4C8A-A6EF-A01D39B712A0}" name="id" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{6291F61B-4873-43E4-9162-99F6F2F333C6}" name="分组" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{A52252C4-214F-4B89-B01D-E9432A19B6ED}" name="类型" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{11F598B0-431B-49D9-9728-E1D34C844DF2}" name="x" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{0656D849-7EB7-4D98-B821-FF0A36ADE155}" name="y" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{A76C9986-5734-44AA-9D58-1C6786054F9C}" name="名称" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{B3E4C7DF-4F0C-43DE-BC3F-24CEB2561749}" name="图片" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{4CB91A3E-B473-4CBC-B361-0E5517581948}" name="前置挂机点列表" dataDxfId="12"/>
+  <tableColumns count="11">
+    <tableColumn id="12" xr3:uid="{5D994712-7AAB-4B73-A5A5-81E04ACECD89}" name="索引" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{B083A4F3-A0E0-4C8A-A6EF-A01D39B712A0}" name="id" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{6291F61B-4873-43E4-9162-99F6F2F333C6}" name="分组" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{A52252C4-214F-4B89-B01D-E9432A19B6ED}" name="类型" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{11F598B0-431B-49D9-9728-E1D34C844DF2}" name="x" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{0656D849-7EB7-4D98-B821-FF0A36ADE155}" name="y" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{29012926-80B9-4C71-B42D-9A8867306D85}" name="品级" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{6D73A5D7-9881-489A-89C0-33C8A1699143}" name="分支" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{A76C9986-5734-44AA-9D58-1C6786054F9C}" name="名称" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{B3E4C7DF-4F0C-43DE-BC3F-24CEB2561749}" name="图片" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{4CB91A3E-B473-4CBC-B361-0E5517581948}" name="前置挂机点列表" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}" name="Cfg_PointPrefix" displayName="Cfg_PointPrefix" ref="A1:E13" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:E13" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}" name="Cfg_PointPrefix" displayName="Cfg_PointPrefix" ref="A1:E14" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:E14" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1054,11 +1063,11 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{9376D5A3-171C-4E34-AC59-47BB73DA3020}" name="索引" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{59C4462A-CCBE-45F4-A86E-6A7726A0EF7E}" name="id" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{F333ABDE-C56E-4401-B6D1-1F3616C8B8F6}" name="分组" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{91C78C23-A14E-4AC7-A13C-66990EFA88A7}" name="需求前置挂机点" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{000FDC8F-AEFC-4D7C-99BB-678D98C9A1A0}" name="需求前置挂机点等级" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{9376D5A3-171C-4E34-AC59-47BB73DA3020}" name="索引" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{59C4462A-CCBE-45F4-A86E-6A7726A0EF7E}" name="id" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{F333ABDE-C56E-4401-B6D1-1F3616C8B8F6}" name="分组" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{91C78C23-A14E-4AC7-A13C-66990EFA88A7}" name="需求前置挂机点" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{000FDC8F-AEFC-4D7C-99BB-678D98C9A1A0}" name="需求前置挂机点等级" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1365,16 +1374,16 @@
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1391,7 +1400,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1405,7 +1426,11 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <f>"MapPoint.行标签["&amp;Cfg_Map[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>MapPoint.行标签[后天].列ID[id]</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1419,53 +1444,49 @@
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f>"挂机点.行标签["&amp;Cfg_Map[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点.行标签[2].列ID[id路径]</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1481,314 +1502,563 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D208725-7EBA-4DAA-ABA3-0228D4508072}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="8" width="4.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="str">
+        <f>$C3&amp;$G3&amp;"品分支"&amp;$H3</f>
+        <v>后天1品分支1</v>
+      </c>
+      <c r="B3" s="1">
+        <f>VLOOKUP($C3,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G3*1000+$H3</f>
+        <v>1001001</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>500</v>
+      </c>
+      <c r="F3" s="1">
+        <f ca="1">RANDBETWEEN(-100,100)</f>
+        <v>62</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天1品分支1</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="str">
+        <f t="shared" ref="A4:A14" si="0">$C4&amp;$G4&amp;"品分支"&amp;$H4</f>
+        <v>后天2品分支1</v>
+      </c>
+      <c r="B4" s="1">
+        <f>VLOOKUP($C4,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G4*1000+$H4</f>
+        <v>1002001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>800</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" ref="F4:F11" ca="1" si="1">RANDBETWEEN(-100,100)</f>
+        <v>51</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天2品分支1</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天2品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天3品分支1</v>
+      </c>
+      <c r="B5" s="1">
+        <f>VLOOKUP($C5,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G5*1000+$H5</f>
+        <v>1003001</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1100</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-14</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天3品分支1</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天3品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天4品分支1</v>
+      </c>
+      <c r="B6" s="1">
+        <f>VLOOKUP($C6,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G6*1000+$H6</f>
+        <v>1004001</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1400</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天4品分支1</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天4品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天5品分支1</v>
+      </c>
+      <c r="B7" s="1">
+        <f>VLOOKUP($C7,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G7*1000+$H7</f>
+        <v>1005001</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1700</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天5品分支1</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天5品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天6品分支1</v>
+      </c>
+      <c r="B8" s="1">
+        <f>VLOOKUP($C8,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G8*1000+$H8</f>
+        <v>1006001</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-6</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天6品分支1</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天6品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天7品分支1</v>
+      </c>
+      <c r="B9" s="1">
+        <f>VLOOKUP($C9,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G9*1000+$H9</f>
+        <v>1007001</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2300</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-16</v>
+      </c>
+      <c r="G9" s="1">
+        <v>7</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天7品分支1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天7品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天8品分支1</v>
+      </c>
+      <c r="B10" s="1">
+        <f>VLOOKUP($C10,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G10*1000+$H10</f>
+        <v>1008001</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-28</v>
+      </c>
+      <c r="G10" s="1">
+        <v>8</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天8品分支1</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天8品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天9品分支1</v>
+      </c>
+      <c r="B11" s="1">
+        <f>VLOOKUP($C11,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G11*1000+$H11</f>
+        <v>1009001</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2900</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" ca="1" si="1"/>
+        <v>-53</v>
+      </c>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天9品分支1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天9品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天10品分支1</v>
+      </c>
+      <c r="B12" s="1">
+        <f>VLOOKUP($C12,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G12*1000+$H12</f>
+        <v>1010001</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3200</v>
+      </c>
+      <c r="F12" s="1">
+        <f ca="1">-300+RANDBETWEEN(-100,100)</f>
+        <v>-269</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天10品分支1</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天10品分支1].列ID[id]</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天10品分支2</v>
+      </c>
+      <c r="B13" s="1">
+        <f>VLOOKUP($C13,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G13*1000+$H13</f>
+        <v>1010002</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3200</v>
+      </c>
+      <c r="F13" s="1">
+        <f ca="1">300+RANDBETWEEN(-100,100)</f>
+        <v>302</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天10品分支2</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天10品分支2].列ID[id]</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>后天11品分支1</v>
+      </c>
+      <c r="B14" s="1">
+        <f>VLOOKUP($C14,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G14*1000+$H14</f>
+        <v>1011001</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3500</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" ref="F14" ca="1" si="2">RANDBETWEEN(-100,100)</f>
+        <v>25</v>
+      </c>
+      <c r="G14" s="1">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="str">
+        <f>Cfg_MapPoint[[#This Row],[索引]]</f>
+        <v>后天11品分支1</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[2].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[3].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[4].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[5].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[6].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[7].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[8].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[9].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[10].列ID[id路径]</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="1">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="1" t="str">
-        <f>"挂机点前置.行标签["&amp;Cfg_MapPoint[[#This Row],[id]]&amp;"].列ID[id路径]"</f>
-        <v>挂机点前置.行标签[11].列ID[id路径]</v>
+      <c r="K14" s="1" t="str">
+        <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
+        <v>PointPrefix.行标签[后天11品分支1].列ID[id]</v>
       </c>
     </row>
   </sheetData>
@@ -1803,10 +2073,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BB87D6-83F9-4B96-8294-2BF3520DB78C}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="1"/>
@@ -1814,224 +2085,239 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天2品分支1to后天1品分支1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_一品to先天_无品</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天3品分支1to后天2品分支1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_一品分支1to先天_无品</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天4品分支1to后天3品分支1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_二品to先天_一品</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天5品分支1to后天4品分支1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_二品to先天_一品分支1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天6品分支1to后天5品分支1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_三品to先天_二品</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天7品分支1to后天6品分支1</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_四品to先天_三品</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天8品分支1to后天7品分支1</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_五品to先天_四品</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天9品分支1to后天8品分支1</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_六品to先天_五品</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天10品分支1to后天9品分支1</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_七品to先天_六品</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天10品分支2to后天9品分支1</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="1" t="str">
-        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_八品to先天_七品</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="1" t="str">
+      <c r="A13" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
-        <v>先天_九品to先天_八品</v>
+        <v>后天11品分支1to后天10品分支1</v>
+      </c>
+      <c r="B13" s="1">
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="str">
+        <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
+        <v>后天11品分支1to后天10品分支2</v>
+      </c>
+      <c r="B14" s="1">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="1">
         <v>10</v>
       </c>
     </row>

--- a/Doc/导出配置/Map.xlsx
+++ b/Doc/导出配置/Map.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD75275-B9A1-419E-85AD-54A0336C1BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8482D6A-BEBB-4498-BD68-2E5E11B89765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Map" sheetId="1" r:id="rId1"/>
     <sheet name="Cfg_MapPoint" sheetId="2" r:id="rId2"/>
     <sheet name="Cfg_PointPrefix" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,10 +29,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{2F0ACF73-673F-48B1-9A1B-183FE5E3A7EB}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FAD60C10-21BE-4044-8418-7AF22B93F668}">
       <text>
         <r>
           <rPr>
@@ -40,11 +40,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-Name
+id
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -52,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{741540A6-1BE7-4087-A506-901A47138171}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{91EB60DE-E415-41E6-B265-58691AEF59F9}">
       <text>
         <r>
           <rPr>
@@ -60,11 +62,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-名称
+name
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -72,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{F208E676-EB64-489F-B488-C2797AC6E556}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{5E0423E2-FE85-4B2C-999E-652EAC88A6D6}">
       <text>
         <r>
           <rPr>
@@ -80,11 +84,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-背景图片
+bg
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -92,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{99F2E9F1-F1AF-48BF-93B1-2F6BD396FC72}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2E931B5C-09B0-47D0-A9C2-FE1752B876DC}">
       <text>
         <r>
           <rPr>
@@ -100,15 +106,21 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-挂机点列表
+pointList
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
-false</t>
+false
+【内容格式】：
+数据名.方法名1[参数1,参数2……].方法名2[参数1,参数2……].…….方法名[Key1=Value1,Key2=Value2]……
+其中参数值如果为默认值可省略，具体方法对应的参数序号和默认值见系统_参数设置的数据表处理方法配置
+如果表头配置的转换关键字配置了方法，此处可只配置数据配置</t>
         </r>
       </text>
     </comment>
@@ -119,10 +131,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{69B1C5DD-0745-4D93-BEFE-F7C0746A648F}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F4A061C6-22AA-4C1E-A5D2-5C7A5B37D39E}">
       <text>
         <r>
           <rPr>
@@ -130,11 +142,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-Name
+id
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -142,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{83E4AF5F-33A1-4621-B4F4-54D58CBC3AFB}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{A2D34E1D-0030-43F5-9184-43909DC35B1F}">
       <text>
         <r>
           <rPr>
@@ -150,11 +164,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-类型
+type
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -162,7 +178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{605F7AE0-C47F-4124-930A-B9249B87C490}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{6399DEF9-641E-4053-912F-EA25BB07C96C}">
       <text>
         <r>
           <rPr>
@@ -170,11 +186,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-名称
+x
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -182,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{3FD22595-2D89-4707-8C08-599ADD0E78F7}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{AE189582-316C-4C9F-8D54-B6A18CF1C1E9}">
       <text>
         <r>
           <rPr>
@@ -190,15 +208,87 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-前置挂机点列表
+y
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
 false</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{748F0197-8E71-421C-9388-5DAA2F8858AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>【字段名】：
+name
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{B96E75AC-D815-441E-8994-3D270CB59632}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>【字段名】：
+icon
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{AB9E2917-A70F-46DB-81C8-044443C4FEDB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>【字段名】：
+prefixPoints
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【内容格式】：
+数据名.方法名1[参数1,参数2……].方法名2[参数1,参数2……].…….方法名[Key1=Value1,Key2=Value2]……
+其中参数值如果为默认值可省略，具体方法对应的参数序号和默认值见系统_参数设置的数据表处理方法配置
+如果表头配置的转换关键字配置了方法，此处可只配置数据配置</t>
         </r>
       </text>
     </comment>
@@ -209,10 +299,10 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{2D0D9EFD-68EA-4045-B552-FAC32170E305}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{54C97502-F09B-4E94-98EF-611B132597BA}">
       <text>
         <r>
           <rPr>
@@ -220,11 +310,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-Name
+id
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -232,7 +324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7CE1A37E-0455-484A-B495-5FEC19B4A195}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{4BE0984A-4F7C-41F2-9FE4-323D217846E4}">
       <text>
         <r>
           <rPr>
@@ -240,21 +332,23 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-挂机点
+prefixPoint
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
 false
 【转换目标字段】
-：挂机点表的id字段</t>
+：MapPoint表的id字段</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{D45481EA-F125-42BD-9FEF-7EFCA5601E01}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{D7D6015B-09A5-4136-A908-9670D60DEF2F}">
       <text>
         <r>
           <rPr>
@@ -262,11 +356,13 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
-挂机点等级
+lv
 【表头】：
+c
 【数据类型】：
 字符
 【为空是否导出】：
@@ -478,6 +574,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -520,6 +617,40 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -539,6 +670,93 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -575,40 +793,6 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -628,93 +812,6 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -734,23 +831,6 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
@@ -772,6 +852,23 @@
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1015,14 +1112,14 @@
     <tableColumn id="1" xr3:uid="{62A7661E-46D3-4FBD-A598-40D05FDEA174}" name="id" dataDxfId="23"/>
     <tableColumn id="2" xr3:uid="{8202C8E8-3ECF-44AC-906A-08BC887BC701}" name="名称" dataDxfId="22"/>
     <tableColumn id="3" xr3:uid="{AA7B6830-77D3-45E0-81B3-CDB5D3D75B6A}" name="背景图片" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{493917F0-DAA9-436F-900A-1A87EE584419}" name="挂机点列表" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{493917F0-DAA9-436F-900A-1A87EE584419}" name="挂机点列表" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}" name="Cfg_MapPoint" displayName="Cfg_MapPoint" ref="A1:K14" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}" name="Cfg_MapPoint" displayName="Cfg_MapPoint" ref="A1:K14" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:K14" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1037,24 +1134,24 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="12" xr3:uid="{5D994712-7AAB-4B73-A5A5-81E04ACECD89}" name="索引" dataDxfId="18"/>
-    <tableColumn id="1" xr3:uid="{B083A4F3-A0E0-4C8A-A6EF-A01D39B712A0}" name="id" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{6291F61B-4873-43E4-9162-99F6F2F333C6}" name="分组" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{A52252C4-214F-4B89-B01D-E9432A19B6ED}" name="类型" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{11F598B0-431B-49D9-9728-E1D34C844DF2}" name="x" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{0656D849-7EB7-4D98-B821-FF0A36ADE155}" name="y" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{29012926-80B9-4C71-B42D-9A8867306D85}" name="品级" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{6D73A5D7-9881-489A-89C0-33C8A1699143}" name="分支" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{A76C9986-5734-44AA-9D58-1C6786054F9C}" name="名称" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{B3E4C7DF-4F0C-43DE-BC3F-24CEB2561749}" name="图片" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{4CB91A3E-B473-4CBC-B361-0E5517581948}" name="前置挂机点列表" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{5D994712-7AAB-4B73-A5A5-81E04ACECD89}" name="索引" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{B083A4F3-A0E0-4C8A-A6EF-A01D39B712A0}" name="id" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{6291F61B-4873-43E4-9162-99F6F2F333C6}" name="分组" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{A52252C4-214F-4B89-B01D-E9432A19B6ED}" name="类型" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{11F598B0-431B-49D9-9728-E1D34C844DF2}" name="x" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{0656D849-7EB7-4D98-B821-FF0A36ADE155}" name="y" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{29012926-80B9-4C71-B42D-9A8867306D85}" name="品级" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{6D73A5D7-9881-489A-89C0-33C8A1699143}" name="分支" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{A76C9986-5734-44AA-9D58-1C6786054F9C}" name="名称" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{B3E4C7DF-4F0C-43DE-BC3F-24CEB2561749}" name="图片" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{4CB91A3E-B473-4CBC-B361-0E5517581948}" name="前置挂机点列表" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}" name="Cfg_PointPrefix" displayName="Cfg_PointPrefix" ref="A1:E14" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}" name="Cfg_PointPrefix" displayName="Cfg_PointPrefix" ref="A1:E14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A1:E14" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1063,11 +1160,11 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{9376D5A3-171C-4E34-AC59-47BB73DA3020}" name="索引" dataDxfId="7"/>
-    <tableColumn id="1" xr3:uid="{59C4462A-CCBE-45F4-A86E-6A7726A0EF7E}" name="id" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{F333ABDE-C56E-4401-B6D1-1F3616C8B8F6}" name="分组" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{91C78C23-A14E-4AC7-A13C-66990EFA88A7}" name="需求前置挂机点" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{000FDC8F-AEFC-4D7C-99BB-678D98C9A1A0}" name="需求前置挂机点等级" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{9376D5A3-171C-4E34-AC59-47BB73DA3020}" name="索引" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{59C4462A-CCBE-45F4-A86E-6A7726A0EF7E}" name="id" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{F333ABDE-C56E-4401-B6D1-1F3616C8B8F6}" name="分组" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{91C78C23-A14E-4AC7-A13C-66990EFA88A7}" name="需求前置挂机点" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{000FDC8F-AEFC-4D7C-99BB-678D98C9A1A0}" name="需求前置挂机点等级" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1371,17 +1468,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3D9014-9428-423D-90DA-50047899F324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1398,7 +1495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1415,7 +1512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1433,7 +1530,7 @@
         <v>MapPoint.行标签[后天].列ID[id]</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1447,7 +1544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1461,7 +1558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1475,7 +1572,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1503,19 +1600,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D208725-7EBA-4DAA-ABA3-0228D4508072}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="4.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="4.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="40.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1550,7 +1647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1585,7 +1682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="str">
         <f>$C3&amp;$G3&amp;"品分支"&amp;$H3</f>
         <v>后天1品分支1</v>
@@ -1601,11 +1698,11 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <f ca="1">RANDBETWEEN(-100,100)</f>
-        <v>62</v>
+        <f ca="1">RANDBETWEEN(-100,100)+500</f>
+        <v>571</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -1621,7 +1718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="str">
         <f t="shared" ref="A4:A14" si="0">$C4&amp;$G4&amp;"品分支"&amp;$H4</f>
         <v>后天2品分支1</v>
@@ -1637,11 +1734,11 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:F11" ca="1" si="1">RANDBETWEEN(-100,100)</f>
-        <v>51</v>
+        <f t="shared" ref="F4:F11" ca="1" si="1">RANDBETWEEN(-100,100)+500</f>
+        <v>565</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
@@ -1661,7 +1758,7 @@
         <v>PointPrefix.行标签[后天2品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天3品分支1</v>
@@ -1677,11 +1774,11 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-14</v>
+        <v>598</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -1701,7 +1798,7 @@
         <v>PointPrefix.行标签[后天3品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天4品分支1</v>
@@ -1717,11 +1814,11 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>495</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -1741,7 +1838,7 @@
         <v>PointPrefix.行标签[后天4品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天5品分支1</v>
@@ -1757,11 +1854,11 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>568</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -1781,7 +1878,7 @@
         <v>PointPrefix.行标签[后天5品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天6品分支1</v>
@@ -1797,11 +1894,11 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-6</v>
+        <v>539</v>
       </c>
       <c r="G8" s="1">
         <v>6</v>
@@ -1821,7 +1918,7 @@
         <v>PointPrefix.行标签[后天6品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天7品分支1</v>
@@ -1837,11 +1934,11 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-16</v>
+        <v>555</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -1861,7 +1958,7 @@
         <v>PointPrefix.行标签[后天7品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天8品分支1</v>
@@ -1877,11 +1974,11 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-28</v>
+        <v>450</v>
       </c>
       <c r="G10" s="1">
         <v>8</v>
@@ -1901,7 +1998,7 @@
         <v>PointPrefix.行标签[后天8品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天9品分支1</v>
@@ -1917,11 +2014,11 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>-53</v>
+        <v>458</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -1941,7 +2038,7 @@
         <v>PointPrefix.行标签[后天9品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天10品分支1</v>
@@ -1957,11 +2054,11 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="F12" s="1">
-        <f ca="1">-300+RANDBETWEEN(-100,100)</f>
-        <v>-269</v>
+        <f ca="1">-300+RANDBETWEEN(-100,100)+500</f>
+        <v>214</v>
       </c>
       <c r="G12" s="1">
         <v>10</v>
@@ -1981,7 +2078,7 @@
         <v>PointPrefix.行标签[后天10品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天10品分支2</v>
@@ -1997,11 +2094,11 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="F13" s="1">
-        <f ca="1">300+RANDBETWEEN(-100,100)</f>
-        <v>302</v>
+        <f ca="1">300+RANDBETWEEN(-100,100)+500</f>
+        <v>754</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -2021,7 +2118,7 @@
         <v>PointPrefix.行标签[后天10品分支2].列ID[id]</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天11品分支1</v>
@@ -2037,11 +2134,11 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" ref="F14" ca="1" si="2">RANDBETWEEN(-100,100)</f>
-        <v>25</v>
+        <f t="shared" ref="F14" ca="1" si="2">RANDBETWEEN(-100,100)+500</f>
+        <v>473</v>
       </c>
       <c r="G14" s="1">
         <v>11</v>
@@ -2074,16 +2171,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BB87D6-83F9-4B96-8294-2BF3520DB78C}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2100,12 +2197,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天2品分支1to后天1品分支1</v>
@@ -2123,7 +2220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天3品分支1to后天2品分支1</v>
@@ -2141,7 +2238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天4品分支1to后天3品分支1</v>
@@ -2159,7 +2256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天5品分支1to后天4品分支1</v>
@@ -2177,7 +2274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天6品分支1to后天5品分支1</v>
@@ -2195,7 +2292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天7品分支1to后天6品分支1</v>
@@ -2213,7 +2310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天8品分支1to后天7品分支1</v>
@@ -2231,7 +2328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天9品分支1to后天8品分支1</v>
@@ -2249,7 +2346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支1to后天9品分支1</v>
@@ -2267,7 +2364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支2to后天9品分支1</v>
@@ -2285,7 +2382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支1</v>
@@ -2303,7 +2400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支2</v>

--- a/Doc/导出配置/Map.xlsx
+++ b/Doc/导出配置/Map.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8482D6A-BEBB-4498-BD68-2E5E11B89765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA1F719-908A-4646-86CD-157D58C35D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Map" sheetId="1" r:id="rId1"/>
     <sheet name="Cfg_MapPoint" sheetId="2" r:id="rId2"/>
     <sheet name="Cfg_PointPrefix" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,10 +29,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FAD60C10-21BE-4044-8418-7AF22B93F668}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{53CBD5C4-37C5-410E-B658-3F18C0F2922D}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{91EB60DE-E415-41E6-B265-58691AEF59F9}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{4C67EDC8-FA5E-4731-8EBA-F1413D0E3442}">
       <text>
         <r>
           <rPr>
@@ -76,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{5E0423E2-FE85-4B2C-999E-652EAC88A6D6}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{1659FDA5-A4B5-4C76-A96E-A37E56A8C2A6}">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2E931B5C-09B0-47D0-A9C2-FE1752B876DC}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{EC39DEF9-2E2C-498E-90D2-F52E072676A5}">
       <text>
         <r>
           <rPr>
@@ -131,10 +131,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{F4A061C6-22AA-4C1E-A5D2-5C7A5B37D39E}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{4D8CA80A-68AF-4688-A1B5-8B60582CA457}">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{A2D34E1D-0030-43F5-9184-43909DC35B1F}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{89960129-44F6-4B29-985A-53C16285C030}">
       <text>
         <r>
           <rPr>
@@ -178,7 +178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{6399DEF9-641E-4053-912F-EA25BB07C96C}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{C3014768-3323-4EAB-B9FE-32EEE540BE9C}">
       <text>
         <r>
           <rPr>
@@ -200,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{AE189582-316C-4C9F-8D54-B6A18CF1C1E9}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{945DE918-F398-4F6C-A43D-27CF55130BCD}">
       <text>
         <r>
           <rPr>
@@ -222,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{748F0197-8E71-421C-9388-5DAA2F8858AE}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{4F15BB71-FD60-4BF0-9186-6A0E406CF008}">
       <text>
         <r>
           <rPr>
@@ -244,7 +244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{B96E75AC-D815-441E-8994-3D270CB59632}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{E4815A48-E212-42C6-8E58-C3E4BD732E31}">
       <text>
         <r>
           <rPr>
@@ -266,7 +266,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{AB9E2917-A70F-46DB-81C8-044443C4FEDB}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{533D3080-05BB-4DBE-A567-2FC9EFCB41CB}">
       <text>
         <r>
           <rPr>
@@ -299,10 +299,10 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{54C97502-F09B-4E94-98EF-611B132597BA}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{885D3A5B-EA55-42A6-8786-9185D44CC0FB}">
       <text>
         <r>
           <rPr>
@@ -324,7 +324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{4BE0984A-4F7C-41F2-9FE4-323D217846E4}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7C6E4D56-61C0-425E-A75C-52ADA93A0EB3}">
       <text>
         <r>
           <rPr>
@@ -348,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{D7D6015B-09A5-4136-A908-9670D60DEF2F}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{32CF085D-E01E-4024-8408-F25970922024}">
       <text>
         <r>
           <rPr>
@@ -1468,17 +1468,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3D9014-9428-423D-90DA-50047899F324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>MapPoint.行标签[后天].列ID[id]</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1600,19 +1600,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D208725-7EBA-4DAA-ABA3-0228D4508072}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="4.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="40.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="4.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>$C3&amp;$G3&amp;"品分支"&amp;$H3</f>
         <v>后天1品分支1</v>
@@ -1698,11 +1698,11 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F3" s="1">
         <f ca="1">RANDBETWEEN(-100,100)+500</f>
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -1718,7 +1718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f t="shared" ref="A4:A14" si="0">$C4&amp;$G4&amp;"品分支"&amp;$H4</f>
         <v>后天2品分支1</v>
@@ -1734,11 +1734,11 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" ref="F4:F11" ca="1" si="1">RANDBETWEEN(-100,100)+500</f>
-        <v>565</v>
+        <v>520</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
@@ -1758,7 +1758,7 @@
         <v>PointPrefix.行标签[后天2品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天3品分支1</v>
@@ -1774,11 +1774,11 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -1798,7 +1798,7 @@
         <v>PointPrefix.行标签[后天3品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天4品分支1</v>
@@ -1814,11 +1814,11 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>495</v>
+        <v>575</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -1838,7 +1838,7 @@
         <v>PointPrefix.行标签[后天4品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天5品分支1</v>
@@ -1854,11 +1854,11 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -1878,7 +1878,7 @@
         <v>PointPrefix.行标签[后天5品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天6品分支1</v>
@@ -1894,11 +1894,11 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>539</v>
+        <v>595</v>
       </c>
       <c r="G8" s="1">
         <v>6</v>
@@ -1918,7 +1918,7 @@
         <v>PointPrefix.行标签[后天6品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天7品分支1</v>
@@ -1934,11 +1934,11 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>555</v>
+        <v>461</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -1958,7 +1958,7 @@
         <v>PointPrefix.行标签[后天7品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天8品分支1</v>
@@ -1974,11 +1974,11 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="F10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>450</v>
+        <v>411</v>
       </c>
       <c r="G10" s="1">
         <v>8</v>
@@ -1998,7 +1998,7 @@
         <v>PointPrefix.行标签[后天8品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天9品分支1</v>
@@ -2014,11 +2014,11 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -2038,7 +2038,7 @@
         <v>PointPrefix.行标签[后天9品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天10品分支1</v>
@@ -2054,11 +2054,11 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="F12" s="1">
         <f ca="1">-300+RANDBETWEEN(-100,100)+500</f>
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="G12" s="1">
         <v>10</v>
@@ -2078,7 +2078,7 @@
         <v>PointPrefix.行标签[后天10品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天10品分支2</v>
@@ -2094,11 +2094,11 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="F13" s="1">
         <f ca="1">300+RANDBETWEEN(-100,100)+500</f>
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -2118,7 +2118,7 @@
         <v>PointPrefix.行标签[后天10品分支2].列ID[id]</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天11品分支1</v>
@@ -2134,11 +2134,11 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="F14" s="1">
         <f t="shared" ref="F14" ca="1" si="2">RANDBETWEEN(-100,100)+500</f>
-        <v>473</v>
+        <v>596</v>
       </c>
       <c r="G14" s="1">
         <v>11</v>
@@ -2171,16 +2171,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BB87D6-83F9-4B96-8294-2BF3520DB78C}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2197,12 +2197,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天2品分支1to后天1品分支1</v>
@@ -2220,7 +2220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天3品分支1to后天2品分支1</v>
@@ -2238,7 +2238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天4品分支1to后天3品分支1</v>
@@ -2256,7 +2256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天5品分支1to后天4品分支1</v>
@@ -2274,7 +2274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天6品分支1to后天5品分支1</v>
@@ -2292,7 +2292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天7品分支1to后天6品分支1</v>
@@ -2310,7 +2310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天8品分支1to后天7品分支1</v>
@@ -2328,7 +2328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天9品分支1to后天8品分支1</v>
@@ -2346,7 +2346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支1to后天9品分支1</v>
@@ -2364,7 +2364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支2to后天9品分支1</v>
@@ -2382,7 +2382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支1</v>
@@ -2400,7 +2400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支2</v>

--- a/Doc/导出配置/Map.xlsx
+++ b/Doc/导出配置/Map.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA1F719-908A-4646-86CD-157D58C35D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C13C270-5F4A-4670-9840-BBB12A026196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Map" sheetId="1" r:id="rId1"/>
     <sheet name="Cfg_MapPoint" sheetId="2" r:id="rId2"/>
     <sheet name="Cfg_PointPrefix" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,10 +29,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{53CBD5C4-37C5-410E-B658-3F18C0F2922D}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{923A3EAC-C402-407C-AFAC-45D6155865A7}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{4C67EDC8-FA5E-4731-8EBA-F1413D0E3442}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{EA15AB56-D47A-423F-9487-CC1E976A21F2}">
       <text>
         <r>
           <rPr>
@@ -76,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{1659FDA5-A4B5-4C76-A96E-A37E56A8C2A6}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{CD6CF362-59D7-468C-93C9-E969FA744204}">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{EC39DEF9-2E2C-498E-90D2-F52E072676A5}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{B13F3882-CA06-4CB5-9765-F8A6A766BE3A}">
       <text>
         <r>
           <rPr>
@@ -131,10 +131,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{4D8CA80A-68AF-4688-A1B5-8B60582CA457}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{DA405CE4-1B65-4617-841B-1AF8CFC84965}">
       <text>
         <r>
           <rPr>
@@ -145,18 +145,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>【字段名】：
-id
-【表头】：
-c
-【数据类型】：
-字符
-【为空是否导出】：
-false</t>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{89960129-44F6-4B29-985A-53C16285C030}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{4CA065A0-C0BE-459C-A61C-7558E179D0EC}">
       <text>
         <r>
           <rPr>
@@ -167,18 +171,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>【字段名】：
-type
-【表头】：
-c
-【数据类型】：
-字符
-【为空是否导出】：
-false</t>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{C3014768-3323-4EAB-B9FE-32EEE540BE9C}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{24FD671A-C13E-47C6-B3D8-C08F3738AECC}">
       <text>
         <r>
           <rPr>
@@ -189,18 +197,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>【字段名】：
-x
-【表头】：
-c
-【数据类型】：
-字符
-【为空是否导出】：
-false</t>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{945DE918-F398-4F6C-A43D-27CF55130BCD}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{E94A8C81-9B3F-4D93-90A6-E03253C2E6D9}">
       <text>
         <r>
           <rPr>
@@ -211,18 +223,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>【字段名】：
-y
-【表头】：
-c
-【数据类型】：
-字符
-【为空是否导出】：
-false</t>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{4F15BB71-FD60-4BF0-9186-6A0E406CF008}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{2DC5763A-2B59-4732-B91A-395CC0C6DDDB}">
       <text>
         <r>
           <rPr>
@@ -233,18 +249,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>【字段名】：
-name
-【表头】：
-c
-【数据类型】：
-字符
-【为空是否导出】：
-false</t>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{E4815A48-E212-42C6-8E58-C3E4BD732E31}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{DD430F85-00A4-4E85-8553-40320A527BBC}">
       <text>
         <r>
           <rPr>
@@ -255,18 +275,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>【字段名】：
-icon
-【表头】：
-c
-【数据类型】：
-字符
-【为空是否导出】：
-false</t>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{533D3080-05BB-4DBE-A567-2FC9EFCB41CB}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{ED4E3CA0-E4B9-409E-B4C0-67B6D3E71E46}">
       <text>
         <r>
           <rPr>
@@ -299,10 +323,10 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{885D3A5B-EA55-42A6-8786-9185D44CC0FB}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{703C8434-2BE3-42F4-A8C6-36695F6CBED4}">
       <text>
         <r>
           <rPr>
@@ -324,7 +348,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7C6E4D56-61C0-425E-A75C-52ADA93A0EB3}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{20EC89C0-B426-4516-81DF-10267A0401B1}">
       <text>
         <r>
           <rPr>
@@ -348,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{32CF085D-E01E-4024-8408-F25970922024}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{9DE81983-B0E2-4CA2-B1C6-530954844A61}">
       <text>
         <r>
           <rPr>
@@ -546,7 +570,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,6 +595,13 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
@@ -1468,17 +1499,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3D9014-9428-423D-90DA-50047899F324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1495,7 +1526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1512,7 +1543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1530,7 +1561,7 @@
         <v>MapPoint.行标签[后天].列ID[id]</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1544,7 +1575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1558,7 +1589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1572,7 +1603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1600,19 +1631,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D208725-7EBA-4DAA-ABA3-0228D4508072}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="4.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="4.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="40.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1647,7 +1678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1682,7 +1713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="str">
         <f>$C3&amp;$G3&amp;"品分支"&amp;$H3</f>
         <v>后天1品分支1</v>
@@ -1702,7 +1733,7 @@
       </c>
       <c r="F3" s="1">
         <f ca="1">RANDBETWEEN(-100,100)+500</f>
-        <v>585</v>
+        <v>414</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -1718,7 +1749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="str">
         <f t="shared" ref="A4:A14" si="0">$C4&amp;$G4&amp;"品分支"&amp;$H4</f>
         <v>后天2品分支1</v>
@@ -1738,7 +1769,7 @@
       </c>
       <c r="F4" s="1">
         <f t="shared" ref="F4:F11" ca="1" si="1">RANDBETWEEN(-100,100)+500</f>
-        <v>520</v>
+        <v>462</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
@@ -1758,7 +1789,7 @@
         <v>PointPrefix.行标签[后天2品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天3品分支1</v>
@@ -1778,7 +1809,7 @@
       </c>
       <c r="F5" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
@@ -1798,7 +1829,7 @@
         <v>PointPrefix.行标签[后天3品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天4品分支1</v>
@@ -1818,7 +1849,7 @@
       </c>
       <c r="F6" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>575</v>
+        <v>409</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -1838,7 +1869,7 @@
         <v>PointPrefix.行标签[后天4品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天5品分支1</v>
@@ -1858,7 +1889,7 @@
       </c>
       <c r="F7" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>589</v>
+        <v>423</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -1878,7 +1909,7 @@
         <v>PointPrefix.行标签[后天5品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天6品分支1</v>
@@ -1898,7 +1929,7 @@
       </c>
       <c r="F8" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>595</v>
+        <v>480</v>
       </c>
       <c r="G8" s="1">
         <v>6</v>
@@ -1918,7 +1949,7 @@
         <v>PointPrefix.行标签[后天6品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天7品分支1</v>
@@ -1938,7 +1969,7 @@
       </c>
       <c r="F9" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -1958,7 +1989,7 @@
         <v>PointPrefix.行标签[后天7品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天8品分支1</v>
@@ -1978,7 +2009,7 @@
       </c>
       <c r="F10" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>411</v>
+        <v>531</v>
       </c>
       <c r="G10" s="1">
         <v>8</v>
@@ -1998,7 +2029,7 @@
         <v>PointPrefix.行标签[后天8品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天9品分支1</v>
@@ -2018,7 +2049,7 @@
       </c>
       <c r="F11" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>425</v>
+        <v>511</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -2038,7 +2069,7 @@
         <v>PointPrefix.行标签[后天9品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天10品分支1</v>
@@ -2058,7 +2089,7 @@
       </c>
       <c r="F12" s="1">
         <f ca="1">-300+RANDBETWEEN(-100,100)+500</f>
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="G12" s="1">
         <v>10</v>
@@ -2078,7 +2109,7 @@
         <v>PointPrefix.行标签[后天10品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天10品分支2</v>
@@ -2098,7 +2129,7 @@
       </c>
       <c r="F13" s="1">
         <f ca="1">300+RANDBETWEEN(-100,100)+500</f>
-        <v>769</v>
+        <v>842</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -2118,7 +2149,7 @@
         <v>PointPrefix.行标签[后天10品分支2].列ID[id]</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>后天11品分支1</v>
@@ -2138,7 +2169,7 @@
       </c>
       <c r="F14" s="1">
         <f t="shared" ref="F14" ca="1" si="2">RANDBETWEEN(-100,100)+500</f>
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="G14" s="1">
         <v>11</v>
@@ -2171,16 +2202,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BB87D6-83F9-4B96-8294-2BF3520DB78C}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="23.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2197,12 +2228,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天2品分支1to后天1品分支1</v>
@@ -2220,7 +2251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天3品分支1to后天2品分支1</v>
@@ -2238,7 +2269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天4品分支1to后天3品分支1</v>
@@ -2256,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天5品分支1to后天4品分支1</v>
@@ -2274,7 +2305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天6品分支1to后天5品分支1</v>
@@ -2292,7 +2323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天7品分支1to后天6品分支1</v>
@@ -2310,7 +2341,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天8品分支1to后天7品分支1</v>
@@ -2328,7 +2359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天9品分支1to后天8品分支1</v>
@@ -2346,7 +2377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支1to后天9品分支1</v>
@@ -2364,7 +2395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支2to后天9品分支1</v>
@@ -2382,7 +2413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支1</v>
@@ -2400,7 +2431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支2</v>

--- a/Doc/导出配置/Map.xlsx
+++ b/Doc/导出配置/Map.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C13C270-5F4A-4670-9840-BBB12A026196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CCDF52-BD57-4D92-96BC-7E986867FBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3A78B3B1-5E3A-410B-8199-1A9F991258E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Map" sheetId="1" r:id="rId1"/>
     <sheet name="Cfg_MapPoint" sheetId="2" r:id="rId2"/>
     <sheet name="Cfg_PointPrefix" sheetId="3" r:id="rId3"/>
+    <sheet name="Cfg_MapPointLevel" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,10 +30,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{923A3EAC-C402-407C-AFAC-45D6155865A7}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{DC435804-0DCA-4B0F-92C5-0C5B447777B1}">
       <text>
         <r>
           <rPr>
@@ -54,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{EA15AB56-D47A-423F-9487-CC1E976A21F2}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{080C5D36-C9C3-48F7-91D3-65F69B27CF39}">
       <text>
         <r>
           <rPr>
@@ -76,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{CD6CF362-59D7-468C-93C9-E969FA744204}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{5225D02C-A6EC-4148-A145-8759485D1272}">
       <text>
         <r>
           <rPr>
@@ -98,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{B13F3882-CA06-4CB5-9765-F8A6A766BE3A}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{20F21434-201B-4DCF-9870-A578A557D35B}">
       <text>
         <r>
           <rPr>
@@ -131,10 +132,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{DA405CE4-1B65-4617-841B-1AF8CFC84965}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FD84489F-2A53-4EB1-972E-2720455700DF}">
       <text>
         <r>
           <rPr>
@@ -145,22 +146,18 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+id
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{4CA065A0-C0BE-459C-A61C-7558E179D0EC}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{326CF1F1-27AE-4BA3-946F-177DFA86E7B7}">
       <text>
         <r>
           <rPr>
@@ -171,22 +168,24 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">【字段名】：
+type
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【枚举值列表】：
+tbl_枚举_地图点类型
+[养成 = 0]：养成
+[战斗 = 1]：战斗
+[商店 = 2]：商店
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{24FD671A-C13E-47C6-B3D8-C08F3738AECC}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{5FA6F435-9C42-4E73-B5EA-167EE8B3B80B}">
       <text>
         <r>
           <rPr>
@@ -197,22 +196,18 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+x
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{E94A8C81-9B3F-4D93-90A6-E03253C2E6D9}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{586A9E4F-8384-4A59-BFFB-1D896755F524}">
       <text>
         <r>
           <rPr>
@@ -223,22 +218,18 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+y
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{2DC5763A-2B59-4732-B91A-395CC0C6DDDB}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{C0BC0CC2-B3EA-4D87-8EC4-266242C724C9}">
       <text>
         <r>
           <rPr>
@@ -249,22 +240,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+scale
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【默认值】：
+1
+【字段描述】：
+点的大小缩放</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{DD430F85-00A4-4E85-8553-40320A527BBC}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{367E34A4-919A-424A-8B07-EC831CC4567F}">
       <text>
         <r>
           <rPr>
@@ -275,22 +266,40 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
+          <t>【字段名】：
+name
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
         </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{C3067CA7-95F3-43F6-87F5-54F5F2CC2129}">
+      <text>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+icon
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{ED4E3CA0-E4B9-409E-B4C0-67B6D3E71E46}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{5F0B18BA-6F89-4612-8579-F7B126697D63}">
       <text>
         <r>
           <rPr>
@@ -323,10 +332,10 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{703C8434-2BE3-42F4-A8C6-36695F6CBED4}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C627F0CD-B8DB-47E7-A6A9-661EE7375349}">
       <text>
         <r>
           <rPr>
@@ -348,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{20EC89C0-B426-4516-81DF-10267A0401B1}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{2905C836-824C-4B75-A02F-55CECC7D182C}">
       <text>
         <r>
           <rPr>
@@ -372,7 +381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{9DE81983-B0E2-4CA2-B1C6-530954844A61}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{386282B2-1759-442A-AE75-A15698F52C14}">
       <text>
         <r>
           <rPr>
@@ -399,7 +408,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="54">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -563,6 +572,28 @@
   </si>
   <si>
     <t>后天11品分支1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗</t>
+  </si>
+  <si>
+    <t>养成</t>
+  </si>
+  <si>
+    <t>缩放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -570,7 +601,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,13 +626,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
@@ -642,7 +666,64 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1130,7 +1211,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C2E19C6-8F99-47B9-A18E-66BEAC16B0C5}" name="Cfg_Map" displayName="Cfg_Map" ref="A1:E7" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C2E19C6-8F99-47B9-A18E-66BEAC16B0C5}" name="Cfg_Map" displayName="Cfg_Map" ref="A1:E7" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A1:E7" xr:uid="{8C2E19C6-8F99-47B9-A18E-66BEAC16B0C5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1139,19 +1220,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="9" xr3:uid="{E6B9AA54-B5B9-4C54-BED2-09D9E8A57723}" name="索引" dataDxfId="24"/>
-    <tableColumn id="1" xr3:uid="{62A7661E-46D3-4FBD-A598-40D05FDEA174}" name="id" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{8202C8E8-3ECF-44AC-906A-08BC887BC701}" name="名称" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{AA7B6830-77D3-45E0-81B3-CDB5D3D75B6A}" name="背景图片" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{493917F0-DAA9-436F-900A-1A87EE584419}" name="挂机点列表" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{E6B9AA54-B5B9-4C54-BED2-09D9E8A57723}" name="索引" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{62A7661E-46D3-4FBD-A598-40D05FDEA174}" name="id" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{8202C8E8-3ECF-44AC-906A-08BC887BC701}" name="名称" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{AA7B6830-77D3-45E0-81B3-CDB5D3D75B6A}" name="背景图片" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{493917F0-DAA9-436F-900A-1A87EE584419}" name="挂机点列表" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}" name="Cfg_MapPoint" displayName="Cfg_MapPoint" ref="A1:K14" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A1:K14" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}" name="Cfg_MapPoint" displayName="Cfg_MapPoint" ref="A1:N14" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:N14" xr:uid="{707C1DAF-3509-4E30-9F7B-4CF9EF030CCD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1163,26 +1244,32 @@
     <filterColumn colId="8" hiddenButton="1"/>
     <filterColumn colId="9" hiddenButton="1"/>
     <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="11">
-    <tableColumn id="12" xr3:uid="{5D994712-7AAB-4B73-A5A5-81E04ACECD89}" name="索引" dataDxfId="17"/>
-    <tableColumn id="1" xr3:uid="{B083A4F3-A0E0-4C8A-A6EF-A01D39B712A0}" name="id" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{6291F61B-4873-43E4-9162-99F6F2F333C6}" name="分组" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{A52252C4-214F-4B89-B01D-E9432A19B6ED}" name="类型" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{11F598B0-431B-49D9-9728-E1D34C844DF2}" name="x" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{0656D849-7EB7-4D98-B821-FF0A36ADE155}" name="y" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{29012926-80B9-4C71-B42D-9A8867306D85}" name="品级" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{6D73A5D7-9881-489A-89C0-33C8A1699143}" name="分支" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{A76C9986-5734-44AA-9D58-1C6786054F9C}" name="名称" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{B3E4C7DF-4F0C-43DE-BC3F-24CEB2561749}" name="图片" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{4CB91A3E-B473-4CBC-B361-0E5517581948}" name="前置挂机点列表" dataDxfId="7"/>
+  <tableColumns count="14">
+    <tableColumn id="12" xr3:uid="{5D994712-7AAB-4B73-A5A5-81E04ACECD89}" name="索引" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{B083A4F3-A0E0-4C8A-A6EF-A01D39B712A0}" name="id" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{6291F61B-4873-43E4-9162-99F6F2F333C6}" name="分组" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{A52252C4-214F-4B89-B01D-E9432A19B6ED}" name="类型" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{11F598B0-431B-49D9-9728-E1D34C844DF2}" name="x" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{0656D849-7EB7-4D98-B821-FF0A36ADE155}" name="y" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{9D96592E-C972-448E-92C5-8E5B15C7FBF6}" name="缩放" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{707D2B1E-23E0-43DB-AE10-A79AEDAD7B16}" name="最大等级" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{29012926-80B9-4C71-B42D-9A8867306D85}" name="品级" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{6D73A5D7-9881-489A-89C0-33C8A1699143}" name="分支" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{A76C9986-5734-44AA-9D58-1C6786054F9C}" name="名称" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{B3E4C7DF-4F0C-43DE-BC3F-24CEB2561749}" name="图片" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{69FA3325-BCA6-47D3-A915-AE38B3E3E424}" name="等级配置" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{4CB91A3E-B473-4CBC-B361-0E5517581948}" name="前置挂机点列表" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}" name="Cfg_PointPrefix" displayName="Cfg_PointPrefix" ref="A1:E14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}" name="Cfg_PointPrefix" displayName="Cfg_PointPrefix" ref="A1:E14" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:E14" xr:uid="{69E8C6B1-6B18-4BE4-B7F2-F992888CE27B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1191,11 +1278,22 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{9376D5A3-171C-4E34-AC59-47BB73DA3020}" name="索引" dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{59C4462A-CCBE-45F4-A86E-6A7726A0EF7E}" name="id" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{F333ABDE-C56E-4401-B6D1-1F3616C8B8F6}" name="分组" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{91C78C23-A14E-4AC7-A13C-66990EFA88A7}" name="需求前置挂机点" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{000FDC8F-AEFC-4D7C-99BB-678D98C9A1A0}" name="需求前置挂机点等级" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{9376D5A3-171C-4E34-AC59-47BB73DA3020}" name="索引" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{59C4462A-CCBE-45F4-A86E-6A7726A0EF7E}" name="id" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{F333ABDE-C56E-4401-B6D1-1F3616C8B8F6}" name="分组" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{91C78C23-A14E-4AC7-A13C-66990EFA88A7}" name="需求前置挂机点" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{000FDC8F-AEFC-4D7C-99BB-678D98C9A1A0}" name="需求前置挂机点等级" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E3CCA7E6-00FA-4506-B4BC-95DA5C74DEAB}" name="Cfg_MapPointLevel" displayName="Cfg_MapPointLevel" ref="A1:B2" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="A1:B2" xr:uid="{E3CCA7E6-00FA-4506-B4BC-95DA5C74DEAB}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9B100979-300A-4986-8874-7B70898AA394}" name="id"/>
+    <tableColumn id="2" xr3:uid="{6476690B-AD4B-4D3F-99A1-027CDB96368A}" name="等级"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1499,17 +1597,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3D9014-9428-423D-90DA-50047899F324}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1526,7 +1624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1543,7 +1641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1561,7 +1659,7 @@
         <v>MapPoint.行标签[后天].列ID[id]</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1575,7 +1673,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1589,7 +1687,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1603,7 +1701,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1630,20 +1728,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D208725-7EBA-4DAA-ABA3-0228D4508072}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="4.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="40.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="4.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1663,22 +1763,31 @@
         <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1697,12 +1806,6 @@
       <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1712,485 +1815,535 @@
       <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
-        <f>$C3&amp;$G3&amp;"品分支"&amp;$H3</f>
+        <f>$C3&amp;$I3&amp;"品分支"&amp;$J3</f>
         <v>后天1品分支1</v>
       </c>
       <c r="B3" s="1">
-        <f>VLOOKUP($C3,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G3*1000+$H3</f>
+        <f>VLOOKUP($C3,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I3*1000+$J3</f>
         <v>1001001</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="1">
-        <v>1</v>
+      <c r="D3" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E3" s="1">
         <v>300</v>
       </c>
       <c r="F3" s="1">
         <f ca="1">RANDBETWEEN(-100,100)+500</f>
-        <v>414</v>
-      </c>
-      <c r="G3" s="1">
+        <v>541</v>
+      </c>
+      <c r="H3" s="1">
+        <v>10</v>
+      </c>
+      <c r="I3" s="1">
         <v>1</v>
       </c>
-      <c r="H3" s="1">
+      <c r="J3" s="1">
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="str">
+      <c r="K3" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天1品分支1</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
-        <f t="shared" ref="A4:A14" si="0">$C4&amp;$G4&amp;"品分支"&amp;$H4</f>
+        <f>$C4&amp;$I4&amp;"品分支"&amp;$J4</f>
         <v>后天2品分支1</v>
       </c>
       <c r="B4" s="1">
-        <f>VLOOKUP($C4,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G4*1000+$H4</f>
+        <f>VLOOKUP($C4,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I4*1000+$J4</f>
         <v>1002001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1">
-        <v>1</v>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="E4" s="1">
         <v>600</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" ref="F4:F11" ca="1" si="1">RANDBETWEEN(-100,100)+500</f>
-        <v>462</v>
+        <f t="shared" ref="F4:F11" ca="1" si="0">RANDBETWEEN(-100,100)+500</f>
+        <v>575</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" s="1">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="I4" s="1" t="str">
+      <c r="K4" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天2品分支1</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="1" t="str">
+      <c r="N4" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天2品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C5&amp;$I5&amp;"品分支"&amp;$J5</f>
         <v>后天3品分支1</v>
       </c>
       <c r="B5" s="1">
-        <f>VLOOKUP($C5,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G5*1000+$H5</f>
+        <f>VLOOKUP($C5,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I5*1000+$J5</f>
         <v>1003001</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="1">
-        <v>1</v>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E5" s="1">
         <v>900</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>566</v>
-      </c>
-      <c r="G5" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>451</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="1">
+      <c r="J5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="str">
+      <c r="K5" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天3品分支1</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="1" t="str">
+      <c r="N5" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天3品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C6&amp;$I6&amp;"品分支"&amp;$J6</f>
         <v>后天4品分支1</v>
       </c>
       <c r="B6" s="1">
-        <f>VLOOKUP($C6,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G6*1000+$H6</f>
+        <f>VLOOKUP($C6,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I6*1000+$J6</f>
         <v>1004001</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E6" s="1">
         <v>1200</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>409</v>
-      </c>
-      <c r="G6" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10</v>
+      </c>
+      <c r="I6" s="1">
         <v>4</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="str">
+      <c r="K6" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天4品分支1</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="1" t="str">
+      <c r="N6" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天4品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C7&amp;$I7&amp;"品分支"&amp;$J7</f>
         <v>后天5品分支1</v>
       </c>
       <c r="B7" s="1">
-        <f>VLOOKUP($C7,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G7*1000+$H7</f>
+        <f>VLOOKUP($C7,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I7*1000+$J7</f>
         <v>1005001</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="1">
-        <v>1</v>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E7" s="1">
         <v>1500</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>423</v>
-      </c>
-      <c r="G7" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>401</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10</v>
+      </c>
+      <c r="I7" s="1">
         <v>5</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="1" t="str">
+      <c r="K7" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天5品分支1</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="1" t="str">
+      <c r="N7" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天5品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C8&amp;$I8&amp;"品分支"&amp;$J8</f>
         <v>后天6品分支1</v>
       </c>
       <c r="B8" s="1">
-        <f>VLOOKUP($C8,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G8*1000+$H8</f>
+        <f>VLOOKUP($C8,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I8*1000+$J8</f>
         <v>1006001</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="1">
-        <v>1</v>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E8" s="1">
         <v>1800</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>480</v>
-      </c>
-      <c r="G8" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>408</v>
+      </c>
+      <c r="H8" s="1">
+        <v>10</v>
+      </c>
+      <c r="I8" s="1">
         <v>6</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="str">
+      <c r="K8" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天6品分支1</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="1" t="str">
+      <c r="N8" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天6品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C9&amp;$I9&amp;"品分支"&amp;$J9</f>
         <v>后天7品分支1</v>
       </c>
       <c r="B9" s="1">
-        <f>VLOOKUP($C9,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G9*1000+$H9</f>
+        <f>VLOOKUP($C9,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I9*1000+$J9</f>
         <v>1007001</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E9" s="1">
         <v>2100</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>457</v>
-      </c>
-      <c r="G9" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>409</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1">
         <v>7</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="K9" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天7品分支1</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="1" t="str">
+      <c r="N9" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天7品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C10&amp;$I10&amp;"品分支"&amp;$J10</f>
         <v>后天8品分支1</v>
       </c>
       <c r="B10" s="1">
-        <f>VLOOKUP($C10,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G10*1000+$H10</f>
+        <f>VLOOKUP($C10,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I10*1000+$J10</f>
         <v>1008001</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="1">
-        <v>1</v>
+      <c r="D10" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E10" s="1">
         <v>2400</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>531</v>
-      </c>
-      <c r="G10" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>444</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
         <v>8</v>
       </c>
-      <c r="H10" s="1">
+      <c r="J10" s="1">
         <v>1</v>
       </c>
-      <c r="I10" s="1" t="str">
+      <c r="K10" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天8品分支1</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="1" t="str">
+      <c r="N10" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天8品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C11&amp;$I11&amp;"品分支"&amp;$J11</f>
         <v>后天9品分支1</v>
       </c>
       <c r="B11" s="1">
-        <f>VLOOKUP($C11,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G11*1000+$H11</f>
+        <f>VLOOKUP($C11,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I11*1000+$J11</f>
         <v>1009001</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E11" s="1">
         <v>2700</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" ca="1" si="1"/>
-        <v>511</v>
-      </c>
-      <c r="G11" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>467</v>
+      </c>
+      <c r="H11" s="1">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1">
         <v>9</v>
       </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="1" t="str">
+      <c r="K11" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天9品分支1</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="1" t="str">
+      <c r="N11" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天9品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C12&amp;$I12&amp;"品分支"&amp;$J12</f>
         <v>后天10品分支1</v>
       </c>
       <c r="B12" s="1">
-        <f>VLOOKUP($C12,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G12*1000+$H12</f>
+        <f>VLOOKUP($C12,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I12*1000+$J12</f>
         <v>1010001</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="1">
-        <v>1</v>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E12" s="1">
         <v>3000</v>
       </c>
       <c r="F12" s="1">
         <f ca="1">-300+RANDBETWEEN(-100,100)+500</f>
-        <v>169</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="H12" s="1">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="1" t="str">
+      <c r="K12" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天10品分支1</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="1" t="str">
+      <c r="N12" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天10品分支1].列ID[id]</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C13&amp;$I13&amp;"品分支"&amp;$J13</f>
         <v>后天10品分支2</v>
       </c>
       <c r="B13" s="1">
-        <f>VLOOKUP($C13,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G13*1000+$H13</f>
+        <f>VLOOKUP($C13,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I13*1000+$J13</f>
         <v>1010002</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
+      <c r="D13" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E13" s="1">
         <v>3000</v>
       </c>
       <c r="F13" s="1">
         <f ca="1">300+RANDBETWEEN(-100,100)+500</f>
-        <v>842</v>
-      </c>
-      <c r="G13" s="1">
-        <v>10</v>
+        <v>885</v>
       </c>
       <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1">
         <v>2</v>
       </c>
-      <c r="I13" s="1" t="str">
+      <c r="K13" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天10品分支2</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K13" s="1" t="str">
+      <c r="N13" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天10品分支2].列ID[id]</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>$C14&amp;$I14&amp;"品分支"&amp;$J14</f>
         <v>后天11品分支1</v>
       </c>
       <c r="B14" s="1">
-        <f>VLOOKUP($C14,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$G14*1000+$H14</f>
+        <f>VLOOKUP($C14,Cfg_Map[],MATCH('Cfg_Map'!$B$1,Cfg_Map[#Headers],0),FALSE)*1000000+$I14*1000+$J14</f>
         <v>1011001</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
+      <c r="D14" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E14" s="1">
         <v>3300</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" ref="F14" ca="1" si="2">RANDBETWEEN(-100,100)+500</f>
-        <v>495</v>
-      </c>
-      <c r="G14" s="1">
+        <f t="shared" ref="F14" ca="1" si="1">RANDBETWEEN(-100,100)+500</f>
+        <v>573</v>
+      </c>
+      <c r="H14" s="1">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1">
         <v>11</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>1</v>
       </c>
-      <c r="I14" s="1" t="str">
+      <c r="K14" s="1" t="str">
         <f>Cfg_MapPoint[[#This Row],[索引]]</f>
         <v>后天11品分支1</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K14" s="1" t="str">
+      <c r="N14" s="1" t="str">
         <f>"PointPrefix.行标签["&amp;Cfg_MapPoint[[#This Row],[索引]]&amp;"].列ID[id]"</f>
         <v>PointPrefix.行标签[后天11品分支1].列ID[id]</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D14" xr:uid="{4B0BC3F7-BB44-4178-944A-CAAAC2E93C3F}">
+      <formula1>"养成,战斗,商店"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
@@ -2202,16 +2355,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56BB87D6-83F9-4B96-8294-2BF3520DB78C}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="23.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2228,12 +2381,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天2品分支1to后天1品分支1</v>
@@ -2251,7 +2404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天3品分支1to后天2品分支1</v>
@@ -2269,7 +2422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天4品分支1to后天3品分支1</v>
@@ -2287,7 +2440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天5品分支1to后天4品分支1</v>
@@ -2305,7 +2458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天6品分支1to后天5品分支1</v>
@@ -2323,7 +2476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天7品分支1to后天6品分支1</v>
@@ -2341,7 +2494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天8品分支1to后天7品分支1</v>
@@ -2359,7 +2512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天9品分支1to后天8品分支1</v>
@@ -2377,7 +2530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支1to后天9品分支1</v>
@@ -2395,7 +2548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天10品分支2to后天9品分支1</v>
@@ -2413,7 +2566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支1</v>
@@ -2431,7 +2584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>Cfg_PointPrefix[[#This Row],[分组]]&amp;"to"&amp;Cfg_PointPrefix[[#This Row],[需求前置挂机点]]</f>
         <v>后天11品分支1to后天10品分支2</v>
@@ -2457,4 +2610,26 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7E7BDD-1E2A-4121-AE95-67D848A36464}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>